--- a/artfynd/A 24235-2024 artfynd.xlsx
+++ b/artfynd/A 24235-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118922424</v>
+        <v>118922443</v>
       </c>
       <c r="B2" t="n">
         <v>56502</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456527</v>
+        <v>456523</v>
       </c>
       <c r="R2" t="n">
-        <v>6705273</v>
+        <v>6705332</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118922383</v>
+        <v>118922366</v>
       </c>
       <c r="B3" t="n">
-        <v>91791</v>
+        <v>91798</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456421</v>
+        <v>456523</v>
       </c>
       <c r="R3" t="n">
-        <v>6705482</v>
+        <v>6705311</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -891,7 +891,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118922443</v>
+        <v>118922424</v>
       </c>
       <c r="B4" t="n">
         <v>56502</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456523</v>
+        <v>456527</v>
       </c>
       <c r="R4" t="n">
-        <v>6705332</v>
+        <v>6705273</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118922278</v>
+        <v>118922383</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>91798</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,25 +1013,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456544</v>
+        <v>456421</v>
       </c>
       <c r="R5" t="n">
-        <v>6705287</v>
+        <v>6705482</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118922306</v>
+        <v>118922278</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456372</v>
+        <v>456544</v>
       </c>
       <c r="R6" t="n">
-        <v>6705485</v>
+        <v>6705287</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1213,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118922366</v>
+        <v>118922306</v>
       </c>
       <c r="B7" t="n">
-        <v>91791</v>
+        <v>78491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,25 +1225,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456523</v>
+        <v>456372</v>
       </c>
       <c r="R7" t="n">
-        <v>6705311</v>
+        <v>6705485</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>

--- a/artfynd/A 24235-2024 artfynd.xlsx
+++ b/artfynd/A 24235-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118922366</v>
+        <v>118922383</v>
       </c>
       <c r="B3" t="n">
         <v>91798</v>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456523</v>
+        <v>456421</v>
       </c>
       <c r="R3" t="n">
-        <v>6705311</v>
+        <v>6705482</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118922383</v>
+        <v>118922278</v>
       </c>
       <c r="B5" t="n">
-        <v>91798</v>
+        <v>78491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,25 +1013,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456421</v>
+        <v>456544</v>
       </c>
       <c r="R5" t="n">
-        <v>6705482</v>
+        <v>6705287</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118922278</v>
+        <v>118922306</v>
       </c>
       <c r="B6" t="n">
         <v>78491</v>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456544</v>
+        <v>456372</v>
       </c>
       <c r="R6" t="n">
-        <v>6705287</v>
+        <v>6705485</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1213,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118922306</v>
+        <v>118922366</v>
       </c>
       <c r="B7" t="n">
-        <v>78491</v>
+        <v>91798</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,25 +1225,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456372</v>
+        <v>456523</v>
       </c>
       <c r="R7" t="n">
-        <v>6705485</v>
+        <v>6705311</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
